--- a/gantt_diagram.xlsx
+++ b/gantt_diagram.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ML\quiz\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\Quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EC93E2D-E969-4FF1-B1C5-A662DA8D90B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BCB812-8F75-42F5-A24C-22D62BFE0846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
+    <workbookView xWindow="3000" yWindow="345" windowWidth="21600" windowHeight="11385" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="gantt-diagram" sheetId="2" r:id="rId1"/>
@@ -592,7 +592,7 @@
       <c r="E4" s="12"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -624,7 +624,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="H6" s="4"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>

--- a/gantt_diagram.xlsx
+++ b/gantt_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\Quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BCB812-8F75-42F5-A24C-22D62BFE0846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91410063-6DE2-4B75-9CD0-82F46659F854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3000" yWindow="345" windowWidth="21600" windowHeight="11385" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
@@ -527,7 +527,7 @@
         <v>46097</v>
       </c>
       <c r="I1" s="1">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -591,9 +591,9 @@
       <c r="D4" s="4"/>
       <c r="E4" s="12"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
+      <c r="I4" s="4"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -609,7 +609,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
+      <c r="I5" s="12"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>

--- a/gantt_diagram.xlsx
+++ b/gantt_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\Quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91410063-6DE2-4B75-9CD0-82F46659F854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BCB812-8F75-42F5-A24C-22D62BFE0846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3000" yWindow="345" windowWidth="21600" windowHeight="11385" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
@@ -527,7 +527,7 @@
         <v>46097</v>
       </c>
       <c r="I1" s="1">
-        <v>46104</v>
+        <v>46101</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -591,9 +591,9 @@
       <c r="D4" s="4"/>
       <c r="E4" s="12"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="4"/>
+      <c r="G4" s="5"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -609,7 +609,7 @@
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="12"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>

--- a/gantt_diagram.xlsx
+++ b/gantt_diagram.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\Quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BCB812-8F75-42F5-A24C-22D62BFE0846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FB1106-F508-4C51-AB84-4259B3C59335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="345" windowWidth="21600" windowHeight="11385" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="gantt-diagram" sheetId="2" r:id="rId1"/>
@@ -527,9 +527,11 @@
         <v>46097</v>
       </c>
       <c r="I1" s="1">
-        <v>46101</v>
-      </c>
-      <c r="J1" s="1"/>
+        <v>46104</v>
+      </c>
+      <c r="J1" s="1">
+        <v>46111</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -593,7 +595,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
+      <c r="I4" s="4"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -609,8 +611,8 @@
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -626,7 +628,7 @@
       <c r="G6" s="5"/>
       <c r="H6" s="4"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="J6" s="12"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>

--- a/gantt_diagram.xlsx
+++ b/gantt_diagram.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\Quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FB1106-F508-4C51-AB84-4259B3C59335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BCB812-8F75-42F5-A24C-22D62BFE0846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
+    <workbookView xWindow="3000" yWindow="345" windowWidth="21600" windowHeight="11385" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="gantt-diagram" sheetId="2" r:id="rId1"/>
@@ -527,11 +527,9 @@
         <v>46097</v>
       </c>
       <c r="I1" s="1">
-        <v>46104</v>
-      </c>
-      <c r="J1" s="1">
-        <v>46111</v>
-      </c>
+        <v>46101</v>
+      </c>
+      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -595,7 +593,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -611,8 +609,8 @@
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -628,7 +626,7 @@
       <c r="G6" s="5"/>
       <c r="H6" s="4"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="12"/>
+      <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>

--- a/gantt_diagram.xlsx
+++ b/gantt_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\Quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FB1106-F508-4C51-AB84-4259B3C59335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6895A236-E96A-4E0E-BBEF-AB1654EB2837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Bejelentkezés</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>Főoldal</t>
+  </si>
+  <si>
+    <t>Css</t>
+  </si>
+  <si>
+    <t>Reszponzivitás</t>
   </si>
 </sst>
 </file>
@@ -170,7 +176,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -178,6 +183,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -532,7 +538,9 @@
       <c r="J1" s="1">
         <v>46111</v>
       </c>
-      <c r="K1" s="1"/>
+      <c r="K1" s="1">
+        <v>46125</v>
+      </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -555,8 +563,8 @@
         <v>0</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -567,7 +575,7 @@
       <c r="M2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -577,7 +585,7 @@
       <c r="D3" s="4"/>
       <c r="E3" s="5"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="11"/>
       <c r="H3" s="4"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -589,9 +597,9 @@
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="11"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="12"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="4"/>
@@ -605,14 +613,14 @@
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="12"/>
+      <c r="C5" s="11"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -621,14 +629,14 @@
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="12"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="4"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="4"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="12"/>
+      <c r="J6" s="11"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -636,7 +644,9 @@
       <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -645,13 +655,16 @@
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
+      <c r="K7" s="11"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -660,7 +673,7 @@
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
-      <c r="K8" s="10"/>
+      <c r="K8" s="13"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -670,8 +683,8 @@
     </row>
     <row r="9" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="9"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
